--- a/artfynd/A 7587-2024 artfynd.xlsx
+++ b/artfynd/A 7587-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311641</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311645</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315958</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314946</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314948</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314950</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314951</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314957</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314961</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314944</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314947</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314949</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314952</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314954</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314955</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314958</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314959</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314962</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314963</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311640</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311642</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311643</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,8 +3347,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311644</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>